--- a/DEV/org.openl.rules.test/test-resources/expected-test-failures/EPBDS-13543_Double_Rounding.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/expected-test-failures/EPBDS-13543_Double_Rounding.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>Steps</t>
   </si>
@@ -90,6 +90,18 @@
   </si>
   <si>
     <t>=System.out.println("Case 1 = "+((Double)$num1).toString()+"  Case2 = "+((Double)$num2).toString())</t>
+  </si>
+  <si>
+    <t>=1 / 3 * 3</t>
+  </si>
+  <si>
+    <t>=9 / 35 * 7</t>
+  </si>
+  <si>
+    <t>=1 / 3 - 0.333333333333333</t>
+  </si>
+  <si>
+    <t>=2 / 3 - 0.666666666666666</t>
   </si>
 </sst>
 </file>
@@ -464,7 +476,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="4:5" x14ac:dyDescent="0.2">
@@ -472,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="4:5" x14ac:dyDescent="0.2"/>
@@ -507,11 +519,11 @@
       <c r="D20" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="E20" t="n" s="0">
-        <v>20.76</v>
-      </c>
-      <c r="F20" t="n" s="0">
-        <v>0.08334</v>
+      <c r="E20" s="0" t="n">
+        <v>3.333333333333333E-16</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>6.666666666666667E-16</v>
       </c>
     </row>
   </sheetData>
